--- a/Documentación/Pruebas comparativas.xlsx
+++ b/Documentación/Pruebas comparativas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unexes-my.sharepoint.com/personal/rmartinrw_alumnos_unex_es/Documents/TFG/Documentación/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_AD4D2F04E46CFB4ACB3E2095D596F110683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF541ABF-B62F-4CB9-AAAC-A0BA718421D7}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="11_AD4D2F04E46CFB4ACB3E2095D596F110683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A8D347-2141-4E29-A0B9-5F6867093EC4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>Paquetería</t>
   </si>
@@ -33,13 +33,7 @@
     <t>Interior de vehículos</t>
   </si>
   <si>
-    <t>Exterior de vehículos</t>
-  </si>
-  <si>
     <t>Personas</t>
-  </si>
-  <si>
-    <t>Habitación</t>
   </si>
   <si>
     <t>Equipaje</t>
@@ -48,16 +42,10 @@
     <t>A-Z</t>
   </si>
   <si>
-    <t>V(min)-Z</t>
-  </si>
-  <si>
     <t>P-Z</t>
   </si>
   <si>
     <t>A-N</t>
-  </si>
-  <si>
-    <t>V(min)-N</t>
   </si>
   <si>
     <t>P-N</t>
@@ -82,6 +70,12 @@
   </si>
   <si>
     <t>Precisión de la E-nose</t>
+  </si>
+  <si>
+    <t>V(s)-Z</t>
+  </si>
+  <si>
+    <t>V(s)-N</t>
   </si>
 </sst>
 </file>
@@ -176,10 +170,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -197,6 +191,3026 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Aciertos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A-Z</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$3:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-99FD-4AC9-8CC5-BFC66BFEA373}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A-N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$3:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-99FD-4AC9-8CC5-BFC66BFEA373}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1965147808"/>
+        <c:axId val="1965152128"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1965147808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1965152128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1965152128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1965147808"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Precisión</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P-Z</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$E$3:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-31D2-4B3B-8D23-DB039CDF0BA3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P-N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$H$3:$H$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-31D2-4B3B-8D23-DB039CDF0BA3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="127082160"/>
+        <c:axId val="127080240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="127082160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="127080240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="127080240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="127082160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Velocidad en segundos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V(s)-Z</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$D$3:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2EBF-454B-9FBF-367832B0DF2B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V(s)-N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$3:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Paquetería</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Interior de vehículos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Personas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Equipaje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$3:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2EBF-454B-9FBF-367832B0DF2B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="130622992"/>
+        <c:axId val="117709280"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="130622992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="117709280"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="117709280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="130622992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>159067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>462915</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6667</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B11BF2DE-9854-D097-36FB-A43F3B25DDCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>50482</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>159067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>488632</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6667</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A70F67F6-7FA2-FC0C-3C86-9D627A34EA12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>40957</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>159067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>212407</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6667</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F3B58E8-8BE8-D560-B82D-820A5FDB994D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,141 +3476,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:K7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>155</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3</v>
+      </c>
       <c r="J3" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>440</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>390</v>
+      </c>
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
       <c r="J5" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>170</v>
+      </c>
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
       <c r="J6" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="J7" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documentación/Pruebas comparativas.xlsx
+++ b/Documentación/Pruebas comparativas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unexes-my.sharepoint.com/personal/rmartinrw_alumnos_unex_es/Documents/TFG/Documentación/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="11_AD4D2F04E46CFB4ACB3E2095D596F110683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A8D347-2141-4E29-A0B9-5F6867093EC4}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="11_AD4D2F04E46CFB4ACB3E2095D596F110683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0554D116-8972-45E0-A206-025F076B6622}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Paquetería</t>
   </si>
@@ -72,10 +72,13 @@
     <t>Precisión de la E-nose</t>
   </si>
   <si>
-    <t>V(s)-Z</t>
+    <t>&gt;</t>
   </si>
   <si>
-    <t>V(s)-N</t>
+    <t>T(s)-Z</t>
+  </si>
+  <si>
+    <t>T(s)-N</t>
   </si>
 </sst>
 </file>
@@ -166,7 +169,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -175,6 +177,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1056,7 +1061,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-ES"/>
-              <a:t>Velocidad en segundos</a:t>
+              <a:t>Tiempo en segundos</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1105,7 +1110,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>V(s)-Z</c:v>
+                  <c:v>T(s)-Z</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1191,7 +1196,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>V(s)-N</c:v>
+                  <c:v>T(s)-N</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3213,6 +3218,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3476,7 +3485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K7"/>
+  <dimension ref="B2:O26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -3485,14 +3494,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -3501,7 +3510,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>7</v>
@@ -3509,7 +3518,7 @@
       <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3517,28 +3526,28 @@
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="7">
         <v>1</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="7">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="7">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="7">
         <v>1</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="7">
         <v>155</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="7">
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3546,28 +3555,28 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="7">
         <v>1</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="7">
         <v>25</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="7">
         <v>10</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="7">
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="7">
         <v>440</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="7">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3575,28 +3584,28 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="7">
         <v>15</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="7">
         <v>10</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="7">
         <v>0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="7">
         <v>390</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="7">
         <v>3</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3604,28 +3613,28 @@
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="7">
         <v>22</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="7">
         <v>10</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="7">
         <v>1</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="7">
         <v>170</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="7">
         <v>10</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3633,8 +3642,13 @@
       <c r="J7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="6" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O26" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
